--- a/submission_giga/Additional_file_7.xlsx
+++ b/submission_giga/Additional_file_7.xlsx
@@ -438,7 +438,8 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Additional file 7. The cross-tissue test with hash-fixed predictions, Section 3.7 of the main text.</t>
+          <t>Additional file 7. The cross-tissue test with hash-fixed predictions, the main-text section Both mechanisms outside kidney: predictions fixed before the
+data.</t>
         </is>
       </c>
     </row>
